--- a/Durability I-V figure/tafel plot alt/Overpotential DATA raw alt/Air BP/30K/Edited/VC Polyol 1.5bp air_unchanged.xlsx
+++ b/Durability I-V figure/tafel plot alt/Overpotential DATA raw alt/Air BP/30K/Edited/VC Polyol 1.5bp air_unchanged.xlsx
@@ -700,7 +700,7 @@
         </is>
       </c>
       <c r="S4" s="0" t="n">
-        <v>-0.547</v>
+        <v>-0.5505</v>
       </c>
       <c r="V4" s="0" t="n">
         <v>-6</v>
@@ -790,7 +790,7 @@
         </is>
       </c>
       <c r="S5" s="0" t="n">
-        <v>-0.0424</v>
+        <v>-0.0444</v>
       </c>
       <c r="V5" s="0" t="n">
         <v>-5.9</v>
